--- a/examples/outputs/Birgo RR Exhibits - Delsan Courtv08.31.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Delsan Courtv08.31.26.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Unit Mix based on # of Beds" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Pres. Rent Roll" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="OneLineRR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Source" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="#0\ &quot;Units&quot;"/>
     <numFmt numFmtId="165" formatCode="#\ &quot;Units&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0\ &quot;SF&quot;"/>
@@ -36,6 +37,8 @@
     <numFmt numFmtId="176" formatCode="mm\/dd\/yyyy"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="180" formatCode="[$-409]m\/d\/yy"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -153,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -387,6 +390,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21317,4 +21324,7405 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W146"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.54296875" customWidth="1" min="1" max="1"/>
+    <col width="1.36328125" customWidth="1" min="2" max="2"/>
+    <col width="3.453125" customWidth="1" min="3" max="3"/>
+    <col width="28.1796875" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="4.1796875" customWidth="1" min="7" max="7"/>
+    <col width="4.08984375" customWidth="1" min="8" max="8"/>
+    <col width="1.54296875" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8.81640625" customWidth="1" min="13" max="13"/>
+    <col width="1.453125" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="8.453125" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="8.453125" customWidth="1" min="18" max="18"/>
+    <col width="7.54296875" customWidth="1" min="19" max="19"/>
+    <col width="5.54296875" customWidth="1" min="20" max="20"/>
+    <col width="1.36328125" customWidth="1" min="22" max="22"/>
+    <col width="4.1796875" customWidth="1" min="23" max="23"/>
+    <col width="5.6328125" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="87" t="inlineStr">
+        <is>
+          <t>Rent Roll Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>Property: Delsan Court</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="87" t="inlineStr">
+        <is>
+          <t>As of 08/31/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>Tenant Name</t>
+        </is>
+      </c>
+      <c r="F5" s="87" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="G5" s="87" t="inlineStr">
+        <is>
+          <t>Unit Type</t>
+        </is>
+      </c>
+      <c r="J5" s="87" t="inlineStr">
+        <is>
+          <t>Sq Ft</t>
+        </is>
+      </c>
+      <c r="K5" s="87" t="inlineStr">
+        <is>
+          <t>Market 
+Rent</t>
+        </is>
+      </c>
+      <c r="L5" s="87" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="M5" s="87" t="inlineStr">
+        <is>
+          <t>Vacancy 
+Loss</t>
+        </is>
+      </c>
+      <c r="N5" s="87" t="inlineStr">
+        <is>
+          <t>Misc 
+Charges</t>
+        </is>
+      </c>
+      <c r="P5" s="87" t="inlineStr">
+        <is>
+          <t>Total 
+Charges</t>
+        </is>
+      </c>
+      <c r="Q5" s="87" t="inlineStr">
+        <is>
+          <t>Security 
+Deposit</t>
+        </is>
+      </c>
+      <c r="R5" s="87" t="inlineStr">
+        <is>
+          <t>Increase 
+Amount</t>
+        </is>
+      </c>
+      <c r="S5" s="87" t="inlineStr">
+        <is>
+          <t>Last Rent 
+Increase</t>
+        </is>
+      </c>
+      <c r="T5" s="87" t="inlineStr">
+        <is>
+          <t>Move 
+In</t>
+        </is>
+      </c>
+      <c r="U5" s="87" t="inlineStr">
+        <is>
+          <t>Move 
+Out</t>
+        </is>
+      </c>
+      <c r="V5" s="87" t="inlineStr">
+        <is>
+          <t>Lease 
+End</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="87" t="inlineStr">
+        <is>
+          <t>Delsan Court</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="87" t="inlineStr">
+        <is>
+          <t>Bly (TSI), Alisha</t>
+        </is>
+      </c>
+      <c r="E7" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J7" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K7" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L7" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="M7" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="Q7" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="R7" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S7" s="87" t="inlineStr">
+        <is>
+          <t>12/23/25</t>
+        </is>
+      </c>
+      <c r="T7" s="90" t="n">
+        <v>46023</v>
+      </c>
+      <c r="V7" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="J8" s="88" t="n">
+        <v>1026</v>
+      </c>
+      <c r="K8" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L8" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M8" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N8" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="87" t="inlineStr">
+        <is>
+          <t>Bryant, Sarah (Belmont)</t>
+        </is>
+      </c>
+      <c r="E9" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" s="87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J9" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K9" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L9" s="89" t="n">
+        <v>1033</v>
+      </c>
+      <c r="M9" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="89" t="n">
+        <v>1033</v>
+      </c>
+      <c r="Q9" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="R9" s="89" t="n">
+        <v>1033</v>
+      </c>
+      <c r="S9" s="87" t="inlineStr">
+        <is>
+          <t>10/24/25</t>
+        </is>
+      </c>
+      <c r="T9" s="90" t="n">
+        <v>45961</v>
+      </c>
+      <c r="V9" s="90" t="n">
+        <v>46691</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="87" t="inlineStr">
+        <is>
+          <t>Sapienza, Jenelle</t>
+        </is>
+      </c>
+      <c r="F10" s="87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="J10" s="88" t="n">
+        <v>1026</v>
+      </c>
+      <c r="K10" s="89" t="n">
+        <v>1345</v>
+      </c>
+      <c r="L10" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="M10" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q10" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="R10" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="S10" s="87" t="inlineStr">
+        <is>
+          <t>03/19/25</t>
+        </is>
+      </c>
+      <c r="T10" s="90" t="n">
+        <v>45747</v>
+      </c>
+      <c r="V10" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="87" t="inlineStr">
+        <is>
+          <t>Boice (RACB), Blake</t>
+        </is>
+      </c>
+      <c r="E11" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" s="87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G11" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J11" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K11" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L11" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="M11" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="Q11" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S11" s="87" t="inlineStr">
+        <is>
+          <t>05/18/26</t>
+        </is>
+      </c>
+      <c r="T11" s="90" t="n">
+        <v>46174</v>
+      </c>
+      <c r="V11" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="87" t="inlineStr">
+        <is>
+          <t>Ricks (BEL), Marickers</t>
+        </is>
+      </c>
+      <c r="E12" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" s="87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G12" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="J12" s="88" t="n">
+        <v>1026</v>
+      </c>
+      <c r="K12" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L12" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M12" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q12" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="S12" s="87" t="inlineStr">
+        <is>
+          <t>08/21/25</t>
+        </is>
+      </c>
+      <c r="T12" s="90" t="n">
+        <v>45901</v>
+      </c>
+      <c r="V12" s="90" t="n">
+        <v>46630</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="87" t="inlineStr">
+        <is>
+          <t>Webb, Darrell</t>
+        </is>
+      </c>
+      <c r="F13" s="87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J13" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K13" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L13" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="M13" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="Q13" s="89" t="n">
+        <v>635</v>
+      </c>
+      <c r="R13" s="89" t="n">
+        <v>80</v>
+      </c>
+      <c r="S13" s="87" t="inlineStr">
+        <is>
+          <t>11/01/24</t>
+        </is>
+      </c>
+      <c r="T13" s="90" t="n">
+        <v>41579</v>
+      </c>
+      <c r="V13" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F14" s="87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="J14" s="88" t="n">
+        <v>1026</v>
+      </c>
+      <c r="K14" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L14" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M14" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N14" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="87" t="inlineStr">
+        <is>
+          <t>Thomas, DeWayne</t>
+        </is>
+      </c>
+      <c r="F15" s="87" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G15" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J15" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K15" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L15" s="89" t="n">
+        <v>950</v>
+      </c>
+      <c r="M15" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="89" t="n">
+        <v>950</v>
+      </c>
+      <c r="Q15" s="89" t="n">
+        <v>475</v>
+      </c>
+      <c r="R15" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="T15" s="90" t="n">
+        <v>42425</v>
+      </c>
+      <c r="V15" s="90" t="n">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="87" t="inlineStr">
+        <is>
+          <t>Rodriguez, Joehan</t>
+        </is>
+      </c>
+      <c r="F16" s="87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G16" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="J16" s="88" t="n">
+        <v>1026</v>
+      </c>
+      <c r="K16" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L16" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="M16" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q16" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="R16" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="S16" s="87" t="inlineStr">
+        <is>
+          <t>03/24/26</t>
+        </is>
+      </c>
+      <c r="T16" s="90" t="n">
+        <v>46111</v>
+      </c>
+      <c r="V16" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="87" t="inlineStr">
+        <is>
+          <t>Simmons, David</t>
+        </is>
+      </c>
+      <c r="F17" s="87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G17" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J17" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K17" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L17" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="M17" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="Q17" s="89" t="n">
+        <v>785</v>
+      </c>
+      <c r="R17" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S17" s="87" t="inlineStr">
+        <is>
+          <t>09/01/25</t>
+        </is>
+      </c>
+      <c r="T17" s="90" t="n">
+        <v>42614</v>
+      </c>
+      <c r="V17" s="90" t="n">
+        <v>46630</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="87" t="inlineStr">
+        <is>
+          <t>Flax (BEL), Julie</t>
+        </is>
+      </c>
+      <c r="E18" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" s="87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G18" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J18" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K18" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L18" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M18" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q18" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="S18" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="T18" s="90" t="n">
+        <v>45811</v>
+      </c>
+      <c r="V18" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="87" t="inlineStr">
+        <is>
+          <t>Adams, Jetaun</t>
+        </is>
+      </c>
+      <c r="F19" s="87" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G19" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J19" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K19" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L19" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M19" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q19" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="R19" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S19" s="87" t="inlineStr">
+        <is>
+          <t>05/29/25</t>
+        </is>
+      </c>
+      <c r="T19" s="90" t="n">
+        <v>45809</v>
+      </c>
+      <c r="V19" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F20" s="87" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G20" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J20" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K20" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L20" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M20" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N20" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="87" t="inlineStr">
+        <is>
+          <t>Dejesus, Ashanti</t>
+        </is>
+      </c>
+      <c r="F21" s="87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G21" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J21" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K21" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L21" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M21" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q21" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S21" s="87" t="inlineStr">
+        <is>
+          <t>03/26/26</t>
+        </is>
+      </c>
+      <c r="T21" s="90" t="n">
+        <v>46155</v>
+      </c>
+      <c r="V21" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="87" t="inlineStr">
+        <is>
+          <t>Novara, Christopher</t>
+        </is>
+      </c>
+      <c r="F22" s="87" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G22" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J22" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K22" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L22" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="M22" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q22" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R22" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="S22" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="T22" s="90" t="n">
+        <v>45427</v>
+      </c>
+      <c r="V22" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="87" t="inlineStr">
+        <is>
+          <t>Watkins, Joanna</t>
+        </is>
+      </c>
+      <c r="F23" s="87" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G23" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J23" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K23" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L23" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M23" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q23" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R23" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="S23" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="T23" s="90" t="n">
+        <v>45031</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="87" t="inlineStr">
+        <is>
+          <t>Brown (RACB), Richard</t>
+        </is>
+      </c>
+      <c r="E24" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" s="87" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G24" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J24" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K24" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L24" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="M24" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="Q24" s="89" t="n">
+        <v>585</v>
+      </c>
+      <c r="R24" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="S24" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="T24" s="90" t="n">
+        <v>41456</v>
+      </c>
+      <c r="V24" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" s="87" t="inlineStr">
+        <is>
+          <t>Washington, Lanaya (RACB)</t>
+        </is>
+      </c>
+      <c r="E25" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="87" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G25" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J25" s="88" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K25" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L25" s="89" t="n">
+        <v>1223</v>
+      </c>
+      <c r="M25" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="89" t="n">
+        <v>1223</v>
+      </c>
+      <c r="Q25" s="89" t="n">
+        <v>1223</v>
+      </c>
+      <c r="R25" s="89" t="n">
+        <v>1223</v>
+      </c>
+      <c r="S25" s="87" t="inlineStr">
+        <is>
+          <t>09/15/25</t>
+        </is>
+      </c>
+      <c r="T25" s="90" t="n">
+        <v>45916</v>
+      </c>
+      <c r="V25" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="87" t="inlineStr">
+        <is>
+          <t>Gloster, Brittany</t>
+        </is>
+      </c>
+      <c r="F26" s="87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G26" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J26" s="88" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K26" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L26" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="M26" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q26" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R26" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="S26" s="87" t="inlineStr">
+        <is>
+          <t>09/23/25</t>
+        </is>
+      </c>
+      <c r="T26" s="90" t="n">
+        <v>45925</v>
+      </c>
+      <c r="V26" s="90" t="n">
+        <v>46660</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="87" t="inlineStr">
+        <is>
+          <t>Pratt, Famatta</t>
+        </is>
+      </c>
+      <c r="F27" s="87" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G27" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J27" s="88" t="n">
+        <v>1076</v>
+      </c>
+      <c r="K27" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L27" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="M27" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Q27" s="89" t="n">
+        <v>800</v>
+      </c>
+      <c r="R27" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S27" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="T27" s="90" t="n">
+        <v>43556</v>
+      </c>
+      <c r="V27" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="87" t="inlineStr">
+        <is>
+          <t>Merriweather, Tonya</t>
+        </is>
+      </c>
+      <c r="F28" s="87" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G28" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J28" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K28" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L28" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="M28" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="P28" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q28" s="89" t="n">
+        <v>585</v>
+      </c>
+      <c r="R28" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S28" s="87" t="inlineStr">
+        <is>
+          <t>05/01/24</t>
+        </is>
+      </c>
+      <c r="T28" s="90" t="n">
+        <v>41395</v>
+      </c>
+      <c r="V28" s="90" t="n">
+        <v>45777</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" s="87" t="inlineStr">
+        <is>
+          <t>Bernier (TSI), Angie</t>
+        </is>
+      </c>
+      <c r="E29" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" s="87" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G29" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J29" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K29" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L29" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M29" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q29" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R29" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S29" s="87" t="inlineStr">
+        <is>
+          <t>12/01/24</t>
+        </is>
+      </c>
+      <c r="T29" s="90" t="n">
+        <v>44516</v>
+      </c>
+      <c r="V29" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F30" s="87" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G30" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J30" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K30" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L30" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M30" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N30" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="87" t="inlineStr">
+        <is>
+          <t>Nix, Terence</t>
+        </is>
+      </c>
+      <c r="F31" s="87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G31" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J31" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K31" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L31" s="89" t="n">
+        <v>825</v>
+      </c>
+      <c r="M31" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="P31" s="89" t="n">
+        <v>1025</v>
+      </c>
+      <c r="Q31" s="89" t="n">
+        <v>585</v>
+      </c>
+      <c r="R31" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S31" s="87" t="inlineStr">
+        <is>
+          <t>01/01/25</t>
+        </is>
+      </c>
+      <c r="T31" s="90" t="n">
+        <v>42856</v>
+      </c>
+      <c r="V31" s="90" t="n">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="87" t="inlineStr">
+        <is>
+          <t>Sandoval, Chelsey</t>
+        </is>
+      </c>
+      <c r="F32" s="87" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G32" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J32" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K32" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L32" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M32" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q32" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R32" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S32" s="87" t="inlineStr">
+        <is>
+          <t>03/23/26</t>
+        </is>
+      </c>
+      <c r="T32" s="90" t="n">
+        <v>46115</v>
+      </c>
+      <c r="V32" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="87" t="inlineStr">
+        <is>
+          <t>Frase, Stephen</t>
+        </is>
+      </c>
+      <c r="F33" s="87" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G33" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J33" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K33" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L33" s="89" t="n">
+        <v>725</v>
+      </c>
+      <c r="M33" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="89" t="n">
+        <v>725</v>
+      </c>
+      <c r="Q33" s="89" t="n">
+        <v>350</v>
+      </c>
+      <c r="R33" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="S33" s="87" t="inlineStr">
+        <is>
+          <t>11/01/24</t>
+        </is>
+      </c>
+      <c r="T33" s="90" t="n">
+        <v>36800</v>
+      </c>
+      <c r="V33" s="90" t="n">
+        <v>46691</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="87" t="inlineStr">
+        <is>
+          <t>Brown, Nardisha</t>
+        </is>
+      </c>
+      <c r="F34" s="87" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G34" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J34" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K34" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L34" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M34" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q34" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R34" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="S34" s="87" t="inlineStr">
+        <is>
+          <t>03/30/26</t>
+        </is>
+      </c>
+      <c r="T34" s="90" t="n">
+        <v>46127</v>
+      </c>
+      <c r="V34" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F35" s="87" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G35" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J35" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K35" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L35" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M35" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N35" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="87" t="inlineStr">
+        <is>
+          <t>Elder (PP), Bobbie jean</t>
+        </is>
+      </c>
+      <c r="E36" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" s="87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G36" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J36" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K36" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L36" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="M36" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q36" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="89" t="n">
+        <v>55</v>
+      </c>
+      <c r="S36" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="T36" s="90" t="n">
+        <v>45231</v>
+      </c>
+      <c r="U36" s="90" t="n">
+        <v>46326</v>
+      </c>
+      <c r="V36" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="87" t="inlineStr">
+        <is>
+          <t>Land (BEL), Starlette</t>
+        </is>
+      </c>
+      <c r="E37" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" s="87" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G37" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J37" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K37" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L37" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="M37" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="Q37" s="89" t="n">
+        <v>635</v>
+      </c>
+      <c r="R37" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="S37" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="T37" s="90" t="n">
+        <v>43132</v>
+      </c>
+      <c r="V37" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="87" t="inlineStr">
+        <is>
+          <t>Gravely (BEL), Jazzlyn</t>
+        </is>
+      </c>
+      <c r="E38" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" s="87" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G38" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J38" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K38" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L38" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M38" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q38" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R38" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="S38" s="87" t="inlineStr">
+        <is>
+          <t>10/27/25</t>
+        </is>
+      </c>
+      <c r="T38" s="90" t="n">
+        <v>45962</v>
+      </c>
+      <c r="V38" s="90" t="n">
+        <v>46691</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="87" t="inlineStr">
+        <is>
+          <t>Marshall, Jonathan</t>
+        </is>
+      </c>
+      <c r="F39" s="87" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G39" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J39" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K39" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L39" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M39" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q39" s="89" t="n">
+        <v>375</v>
+      </c>
+      <c r="R39" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S39" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="T39" s="90" t="n">
+        <v>38018</v>
+      </c>
+      <c r="V39" s="90" t="n">
+        <v>46660</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="87" t="inlineStr">
+        <is>
+          <t>Drayton, Rayshel</t>
+        </is>
+      </c>
+      <c r="F40" s="87" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G40" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J40" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K40" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L40" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M40" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q40" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R40" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S40" s="87" t="inlineStr">
+        <is>
+          <t>05/12/25</t>
+        </is>
+      </c>
+      <c r="T40" s="90" t="n">
+        <v>45792</v>
+      </c>
+      <c r="V40" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="87" t="inlineStr">
+        <is>
+          <t>Simmons-Mallory, Kimberly</t>
+        </is>
+      </c>
+      <c r="F41" s="87" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G41" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J41" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K41" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L41" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="M41" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="Q41" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="S41" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="T41" s="90" t="n">
+        <v>42227</v>
+      </c>
+      <c r="V41" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" s="87" t="inlineStr">
+        <is>
+          <t>Dejesus, Jamira</t>
+        </is>
+      </c>
+      <c r="F42" s="87" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G42" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J42" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K42" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L42" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M42" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q42" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S42" s="87" t="inlineStr">
+        <is>
+          <t>04/09/26</t>
+        </is>
+      </c>
+      <c r="T42" s="90" t="n">
+        <v>46143</v>
+      </c>
+      <c r="V42" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="87" t="inlineStr">
+        <is>
+          <t>Copland (TSI), Christopher</t>
+        </is>
+      </c>
+      <c r="E43" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F43" s="87" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G43" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J43" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K43" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L43" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M43" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q43" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R43" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S43" s="87" t="inlineStr">
+        <is>
+          <t>12/01/24</t>
+        </is>
+      </c>
+      <c r="T43" s="90" t="n">
+        <v>44516</v>
+      </c>
+      <c r="V43" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="87" t="inlineStr">
+        <is>
+          <t>Mazhindu, Timothy</t>
+        </is>
+      </c>
+      <c r="F44" s="87" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G44" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J44" s="88" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K44" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L44" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="M44" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q44" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R44" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S44" s="87" t="inlineStr">
+        <is>
+          <t>07/01/25</t>
+        </is>
+      </c>
+      <c r="T44" s="90" t="n">
+        <v>45457</v>
+      </c>
+      <c r="V44" s="90" t="n">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" s="87" t="inlineStr">
+        <is>
+          <t>Rosado (BEL), Iraisa</t>
+        </is>
+      </c>
+      <c r="E45" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" s="87" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G45" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J45" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K45" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L45" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M45" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q45" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R45" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S45" s="87" t="inlineStr">
+        <is>
+          <t>05/29/25</t>
+        </is>
+      </c>
+      <c r="T45" s="90" t="n">
+        <v>45807</v>
+      </c>
+      <c r="V45" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F46" s="87" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G46" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J46" s="88" t="n">
+        <v>1076</v>
+      </c>
+      <c r="K46" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L46" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M46" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="N46" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="87" t="inlineStr">
+        <is>
+          <t>Anderson BMHA, Nicole</t>
+        </is>
+      </c>
+      <c r="E47" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" s="87" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G47" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J47" s="88" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K47" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L47" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M47" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q47" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="S47" s="87" t="inlineStr">
+        <is>
+          <t>07/17/26</t>
+        </is>
+      </c>
+      <c r="T47" s="90" t="n">
+        <v>46220</v>
+      </c>
+      <c r="V47" s="90" t="n">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="87" t="inlineStr">
+        <is>
+          <t>Brown, Darius</t>
+        </is>
+      </c>
+      <c r="F48" s="87" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G48" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J48" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K48" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L48" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="M48" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Q48" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="S48" s="87" t="inlineStr">
+        <is>
+          <t>01/19/26</t>
+        </is>
+      </c>
+      <c r="T48" s="90" t="n">
+        <v>46081</v>
+      </c>
+      <c r="V48" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" s="87" t="inlineStr">
+        <is>
+          <t>Nyamuke, Adoni</t>
+        </is>
+      </c>
+      <c r="F49" s="87" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G49" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J49" s="88" t="n">
+        <v>940</v>
+      </c>
+      <c r="K49" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L49" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="M49" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="Q49" s="89" t="n">
+        <v>925</v>
+      </c>
+      <c r="R49" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S49" s="87" t="inlineStr">
+        <is>
+          <t>11/01/24</t>
+        </is>
+      </c>
+      <c r="T49" s="90" t="n">
+        <v>44113</v>
+      </c>
+      <c r="V49" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="87" t="inlineStr">
+        <is>
+          <t>Gregory, Shanay</t>
+        </is>
+      </c>
+      <c r="F50" s="87" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G50" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J50" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K50" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L50" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M50" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q50" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R50" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S50" s="87" t="inlineStr">
+        <is>
+          <t>05/15/26</t>
+        </is>
+      </c>
+      <c r="T50" s="90" t="n">
+        <v>46188</v>
+      </c>
+      <c r="V50" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="87" t="inlineStr">
+        <is>
+          <t>Sessum, Brittany</t>
+        </is>
+      </c>
+      <c r="F51" s="87" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G51" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J51" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K51" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L51" s="89" t="n">
+        <v>1395</v>
+      </c>
+      <c r="M51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="89" t="n">
+        <v>1395</v>
+      </c>
+      <c r="Q51" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R51" s="89" t="n">
+        <v>45</v>
+      </c>
+      <c r="S51" s="87" t="inlineStr">
+        <is>
+          <t>01/01/26</t>
+        </is>
+      </c>
+      <c r="T51" s="90" t="n">
+        <v>44564</v>
+      </c>
+      <c r="V51" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" s="87" t="inlineStr">
+        <is>
+          <t>Osby, Tierra</t>
+        </is>
+      </c>
+      <c r="F52" s="87" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G52" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J52" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K52" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L52" s="89" t="n">
+        <v>1025</v>
+      </c>
+      <c r="M52" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="89" t="n">
+        <v>1025</v>
+      </c>
+      <c r="Q52" s="89" t="n">
+        <v>660</v>
+      </c>
+      <c r="R52" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S52" s="87" t="inlineStr">
+        <is>
+          <t>07/01/24</t>
+        </is>
+      </c>
+      <c r="T52" s="90" t="n">
+        <v>42781</v>
+      </c>
+      <c r="U52" s="90" t="n">
+        <v>46295</v>
+      </c>
+      <c r="V52" s="90" t="n">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" s="87" t="inlineStr">
+        <is>
+          <t>White (BEL), Kimberly</t>
+        </is>
+      </c>
+      <c r="E53" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" s="87" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G53" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J53" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K53" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L53" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="M53" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="Q53" s="89" t="n">
+        <v>745</v>
+      </c>
+      <c r="R53" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S53" s="87" t="inlineStr">
+        <is>
+          <t>02/01/25</t>
+        </is>
+      </c>
+      <c r="T53" s="90" t="n">
+        <v>42095</v>
+      </c>
+      <c r="V53" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" s="87" t="inlineStr">
+        <is>
+          <t>Meadows, Torriana</t>
+        </is>
+      </c>
+      <c r="F54" s="87" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G54" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J54" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K54" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L54" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M54" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q54" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R54" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S54" s="87" t="inlineStr">
+        <is>
+          <t>05/08/26</t>
+        </is>
+      </c>
+      <c r="T54" s="90" t="n">
+        <v>46174</v>
+      </c>
+      <c r="V54" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" s="87" t="inlineStr">
+        <is>
+          <t>Proctor (BEL), Reona</t>
+        </is>
+      </c>
+      <c r="E55" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F55" s="87" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G55" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J55" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K55" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L55" s="89" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M55" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="89" t="n">
+        <v>1230</v>
+      </c>
+      <c r="Q55" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R55" s="89" t="n">
+        <v>1230</v>
+      </c>
+      <c r="S55" s="87" t="inlineStr">
+        <is>
+          <t>03/05/25</t>
+        </is>
+      </c>
+      <c r="T55" s="90" t="n">
+        <v>45722</v>
+      </c>
+      <c r="V55" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="87" t="inlineStr">
+        <is>
+          <t>Carter, Christina</t>
+        </is>
+      </c>
+      <c r="F56" s="87" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G56" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J56" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K56" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L56" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="M56" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="Q56" s="89" t="n">
+        <v>595</v>
+      </c>
+      <c r="R56" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S56" s="87" t="inlineStr">
+        <is>
+          <t>12/01/25</t>
+        </is>
+      </c>
+      <c r="T56" s="90" t="n">
+        <v>43435</v>
+      </c>
+      <c r="V56" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="87" t="inlineStr">
+        <is>
+          <t>Seagroves, Sam</t>
+        </is>
+      </c>
+      <c r="F57" s="87" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G57" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J57" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K57" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L57" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q57" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R57" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="S57" s="87" t="inlineStr">
+        <is>
+          <t>02/01/26</t>
+        </is>
+      </c>
+      <c r="T57" s="90" t="n">
+        <v>45684</v>
+      </c>
+      <c r="V57" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" s="87" t="inlineStr">
+        <is>
+          <t>Thornton (BMHA), Chanel</t>
+        </is>
+      </c>
+      <c r="E58" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F58" s="87" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G58" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J58" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K58" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L58" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M58" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="P58" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="Q58" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R58" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S58" s="87" t="inlineStr">
+        <is>
+          <t>10/11/24</t>
+        </is>
+      </c>
+      <c r="T58" s="90" t="n">
+        <v>45576</v>
+      </c>
+      <c r="V58" s="90" t="n">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="87" t="inlineStr">
+        <is>
+          <t>McMillan, Taijanay</t>
+        </is>
+      </c>
+      <c r="F59" s="87" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G59" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J59" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K59" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L59" s="89" t="n">
+        <v>1315</v>
+      </c>
+      <c r="M59" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="P59" s="89" t="n">
+        <v>1340</v>
+      </c>
+      <c r="Q59" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R59" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="S59" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="T59" s="90" t="n">
+        <v>45198</v>
+      </c>
+      <c r="V59" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="87" t="inlineStr">
+        <is>
+          <t>Grabowski (TSI), Ariana</t>
+        </is>
+      </c>
+      <c r="E60" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F60" s="87" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G60" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J60" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K60" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L60" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M60" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q60" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R60" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S60" s="87" t="inlineStr">
+        <is>
+          <t>12/01/24</t>
+        </is>
+      </c>
+      <c r="T60" s="90" t="n">
+        <v>44515</v>
+      </c>
+      <c r="V60" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="87" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G61" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J61" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K61" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L61" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M61" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="N61" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F62" s="87" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G62" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J62" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K62" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L62" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M62" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="N62" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" s="87" t="inlineStr">
+        <is>
+          <t>Harden, Crystal</t>
+        </is>
+      </c>
+      <c r="F63" s="87" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G63" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J63" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K63" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L63" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="M63" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="Q63" s="89" t="n">
+        <v>850</v>
+      </c>
+      <c r="R63" s="89" t="n">
+        <v>80</v>
+      </c>
+      <c r="S63" s="87" t="inlineStr">
+        <is>
+          <t>09/01/25</t>
+        </is>
+      </c>
+      <c r="T63" s="90" t="n">
+        <v>44028</v>
+      </c>
+      <c r="V63" s="90" t="n">
+        <v>46630</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" s="87" t="inlineStr">
+        <is>
+          <t>Otero, Gladys</t>
+        </is>
+      </c>
+      <c r="F64" s="87" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G64" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J64" s="88" t="n">
+        <v>1076</v>
+      </c>
+      <c r="K64" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L64" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="M64" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q64" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R64" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="S64" s="87" t="inlineStr">
+        <is>
+          <t>04/11/25</t>
+        </is>
+      </c>
+      <c r="T64" s="90" t="n">
+        <v>45762</v>
+      </c>
+      <c r="V64" s="90" t="n">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" s="87" t="inlineStr">
+        <is>
+          <t>Szatkowski, Janay</t>
+        </is>
+      </c>
+      <c r="F65" s="87" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G65" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J65" s="88" t="n">
+        <v>1076</v>
+      </c>
+      <c r="K65" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L65" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M65" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q65" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="S65" s="87" t="inlineStr">
+        <is>
+          <t>01/01/26</t>
+        </is>
+      </c>
+      <c r="T65" s="90" t="n">
+        <v>44896</v>
+      </c>
+      <c r="V65" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="87" t="inlineStr">
+        <is>
+          <t>Prince, Nathen</t>
+        </is>
+      </c>
+      <c r="F66" s="87" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G66" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J66" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K66" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L66" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M66" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q66" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R66" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S66" s="87" t="inlineStr">
+        <is>
+          <t>05/22/25</t>
+        </is>
+      </c>
+      <c r="T66" s="90" t="n">
+        <v>45834</v>
+      </c>
+      <c r="V66" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="87" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G67" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J67" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K67" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L67" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M67" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N67" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" s="87" t="inlineStr">
+        <is>
+          <t>Woods, Startrise</t>
+        </is>
+      </c>
+      <c r="F68" s="87" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G68" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J68" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K68" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L68" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M68" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q68" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R68" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="S68" s="87" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+      <c r="T68" s="90" t="n">
+        <v>46234</v>
+      </c>
+      <c r="V68" s="90" t="n">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" s="87" t="inlineStr">
+        <is>
+          <t>Maciejewski (TSI), Bruce</t>
+        </is>
+      </c>
+      <c r="E69" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F69" s="87" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G69" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J69" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K69" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L69" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M69" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q69" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R69" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S69" s="87" t="inlineStr">
+        <is>
+          <t>12/01/24</t>
+        </is>
+      </c>
+      <c r="T69" s="90" t="n">
+        <v>44516</v>
+      </c>
+      <c r="V69" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" s="87" t="inlineStr">
+        <is>
+          <t>Negron, Brittney</t>
+        </is>
+      </c>
+      <c r="F70" s="87" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G70" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J70" s="88" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K70" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L70" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="M70" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q70" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R70" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="S70" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="T70" s="90" t="n">
+        <v>45596</v>
+      </c>
+      <c r="V70" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" s="87" t="inlineStr">
+        <is>
+          <t>Williams, Linda</t>
+        </is>
+      </c>
+      <c r="F71" s="87" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G71" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J71" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K71" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L71" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="M71" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="Q71" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S71" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="T71" s="90" t="n">
+        <v>41913</v>
+      </c>
+      <c r="V71" s="90" t="n">
+        <v>46660</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" s="87" t="inlineStr">
+        <is>
+          <t>Jones, Michelle</t>
+        </is>
+      </c>
+      <c r="F72" s="87" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G72" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J72" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K72" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L72" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="M72" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="Q72" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R72" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="S72" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="T72" s="90" t="n">
+        <v>44671</v>
+      </c>
+      <c r="V72" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F73" s="87" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G73" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J73" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K73" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L73" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M73" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N73" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" s="87" t="inlineStr">
+        <is>
+          <t>Smith, Arianna</t>
+        </is>
+      </c>
+      <c r="F74" s="87" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G74" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J74" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K74" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L74" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M74" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q74" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R74" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S74" s="87" t="inlineStr">
+        <is>
+          <t>03/26/25</t>
+        </is>
+      </c>
+      <c r="T74" s="90" t="n">
+        <v>45751</v>
+      </c>
+      <c r="V74" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" s="87" t="inlineStr">
+        <is>
+          <t>Martinez-Santana, Raysa</t>
+        </is>
+      </c>
+      <c r="F75" s="87" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G75" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J75" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K75" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L75" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M75" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q75" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R75" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S75" s="87" t="inlineStr">
+        <is>
+          <t>03/27/26</t>
+        </is>
+      </c>
+      <c r="T75" s="90" t="n">
+        <v>46162</v>
+      </c>
+      <c r="V75" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" s="87" t="inlineStr">
+        <is>
+          <t>Burgio, Monet</t>
+        </is>
+      </c>
+      <c r="F76" s="87" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G76" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J76" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K76" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L76" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="M76" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q76" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R76" s="89" t="n">
+        <v>80</v>
+      </c>
+      <c r="S76" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="T76" s="90" t="n">
+        <v>45184</v>
+      </c>
+      <c r="V76" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" s="87" t="inlineStr">
+        <is>
+          <t>May (RACB), John</t>
+        </is>
+      </c>
+      <c r="E77" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F77" s="87" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G77" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J77" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K77" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L77" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="M77" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q77" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="89" t="n">
+        <v>80</v>
+      </c>
+      <c r="S77" s="87" t="inlineStr">
+        <is>
+          <t>09/01/25</t>
+        </is>
+      </c>
+      <c r="T77" s="90" t="n">
+        <v>45536</v>
+      </c>
+      <c r="V77" s="90" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" s="87" t="inlineStr">
+        <is>
+          <t>Services Inc, Transitional</t>
+        </is>
+      </c>
+      <c r="F78" s="87" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G78" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J78" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K78" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L78" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M78" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q78" s="89" t="n">
+        <v>755</v>
+      </c>
+      <c r="R78" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S78" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="T78" s="90" t="n">
+        <v>41030</v>
+      </c>
+      <c r="V78" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" s="87" t="inlineStr">
+        <is>
+          <t>Delgado, Narraly</t>
+        </is>
+      </c>
+      <c r="F79" s="87" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G79" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J79" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K79" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L79" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="M79" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="Q79" s="89" t="n">
+        <v>850</v>
+      </c>
+      <c r="R79" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S79" s="87" t="inlineStr">
+        <is>
+          <t>05/01/24</t>
+        </is>
+      </c>
+      <c r="T79" s="90" t="n">
+        <v>44235</v>
+      </c>
+      <c r="V79" s="90" t="n">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" s="87" t="inlineStr">
+        <is>
+          <t>Watkins, Kathleen</t>
+        </is>
+      </c>
+      <c r="F80" s="87" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G80" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J80" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K80" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L80" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M80" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q80" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R80" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="S80" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="T80" s="90" t="n">
+        <v>45047</v>
+      </c>
+      <c r="V80" s="90" t="n">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="87" t="inlineStr">
+        <is>
+          <t>Millington, Chevaneese</t>
+        </is>
+      </c>
+      <c r="F81" s="87" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G81" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J81" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K81" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L81" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M81" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q81" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R81" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S81" s="87" t="inlineStr">
+        <is>
+          <t>05/27/25</t>
+        </is>
+      </c>
+      <c r="T81" s="90" t="n">
+        <v>45807</v>
+      </c>
+      <c r="V81" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" s="87" t="inlineStr">
+        <is>
+          <t>Jackson (BEL), Alyshia</t>
+        </is>
+      </c>
+      <c r="E82" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F82" s="87" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G82" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J82" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K82" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L82" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M82" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q82" s="89" t="n">
+        <v>850</v>
+      </c>
+      <c r="R82" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S82" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="T82" s="90" t="n">
+        <v>43719</v>
+      </c>
+      <c r="V82" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" s="87" t="inlineStr">
+        <is>
+          <t>Miles, Shawn</t>
+        </is>
+      </c>
+      <c r="F83" s="87" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G83" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J83" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K83" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L83" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="M83" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="Q83" s="89" t="n">
+        <v>400</v>
+      </c>
+      <c r="R83" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S83" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="T83" s="90" t="n">
+        <v>39295</v>
+      </c>
+      <c r="V83" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" s="87" t="inlineStr">
+        <is>
+          <t>Rivera (BMHA), Katherine</t>
+        </is>
+      </c>
+      <c r="E84" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F84" s="87" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G84" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J84" s="88" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K84" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L84" s="89" t="n">
+        <v>1525</v>
+      </c>
+      <c r="M84" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="89" t="n">
+        <v>1525</v>
+      </c>
+      <c r="Q84" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="R84" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S84" s="87" t="inlineStr">
+        <is>
+          <t>07/01/25</t>
+        </is>
+      </c>
+      <c r="T84" s="90" t="n">
+        <v>45467</v>
+      </c>
+      <c r="V84" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" s="87" t="inlineStr">
+        <is>
+          <t>Hidalgo, Evelyn</t>
+        </is>
+      </c>
+      <c r="F85" s="87" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G85" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J85" s="88" t="n">
+        <v>1076</v>
+      </c>
+      <c r="K85" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="L85" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="M85" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="Q85" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R85" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S85" s="87" t="inlineStr">
+        <is>
+          <t>09/01/25</t>
+        </is>
+      </c>
+      <c r="T85" s="90" t="n">
+        <v>40421</v>
+      </c>
+      <c r="V85" s="90" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" s="87" t="inlineStr">
+        <is>
+          <t>Pilgrom, Jairus</t>
+        </is>
+      </c>
+      <c r="F86" s="87" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G86" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J86" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K86" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L86" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M86" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q86" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R86" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S86" s="87" t="inlineStr">
+        <is>
+          <t>04/17/26</t>
+        </is>
+      </c>
+      <c r="T86" s="90" t="n">
+        <v>46143</v>
+      </c>
+      <c r="V86" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" s="87" t="inlineStr">
+        <is>
+          <t>Robinson-Peoples (BMHA), Ciara</t>
+        </is>
+      </c>
+      <c r="E87" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F87" s="87" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G87" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J87" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K87" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L87" s="89" t="n">
+        <v>1245</v>
+      </c>
+      <c r="M87" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="89" t="n">
+        <v>1245</v>
+      </c>
+      <c r="Q87" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="89" t="n">
+        <v>1245</v>
+      </c>
+      <c r="S87" s="87" t="inlineStr">
+        <is>
+          <t>03/10/25</t>
+        </is>
+      </c>
+      <c r="T87" s="90" t="n">
+        <v>45726</v>
+      </c>
+      <c r="U87" s="90" t="n">
+        <v>46387</v>
+      </c>
+      <c r="V87" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" s="87" t="inlineStr">
+        <is>
+          <t>Wigdor (RACB), Rachel</t>
+        </is>
+      </c>
+      <c r="E88" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F88" s="87" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G88" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J88" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K88" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L88" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M88" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q88" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="S88" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="T88" s="90" t="n">
+        <v>45359</v>
+      </c>
+      <c r="V88" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" s="87" t="inlineStr">
+        <is>
+          <t>Lofton (BEL), Chinira</t>
+        </is>
+      </c>
+      <c r="E89" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F89" s="87" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G89" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J89" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K89" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L89" s="89" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M89" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="89" t="n">
+        <v>1230</v>
+      </c>
+      <c r="Q89" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="89" t="n">
+        <v>1230</v>
+      </c>
+      <c r="S89" s="87" t="inlineStr">
+        <is>
+          <t>11/25/24</t>
+        </is>
+      </c>
+      <c r="T89" s="90" t="n">
+        <v>45621</v>
+      </c>
+      <c r="V89" s="90" t="n">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" s="87" t="inlineStr">
+        <is>
+          <t>Lindsay, Nosa'J</t>
+        </is>
+      </c>
+      <c r="F90" s="87" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G90" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J90" s="88" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K90" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L90" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="M90" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q90" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R90" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S90" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="T90" s="90" t="n">
+        <v>45565</v>
+      </c>
+      <c r="U90" s="90" t="n">
+        <v>46286</v>
+      </c>
+      <c r="V90" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" s="87" t="inlineStr">
+        <is>
+          <t>Freeman (BFNC), Ebin</t>
+        </is>
+      </c>
+      <c r="E91" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F91" s="87" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G91" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J91" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K91" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L91" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M91" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q91" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R91" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="S91" s="87" t="inlineStr">
+        <is>
+          <t>07/03/25</t>
+        </is>
+      </c>
+      <c r="T91" s="90" t="n">
+        <v>45853</v>
+      </c>
+      <c r="V91" s="90" t="n">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="C92" s="87" t="inlineStr">
+        <is>
+          <t>Rosario, Jose</t>
+        </is>
+      </c>
+      <c r="F92" s="87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G92" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J92" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K92" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L92" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="M92" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Q92" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R92" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="S92" s="87" t="inlineStr">
+        <is>
+          <t>12/01/24</t>
+        </is>
+      </c>
+      <c r="T92" s="90" t="n">
+        <v>45243</v>
+      </c>
+      <c r="V92" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="C93" s="87" t="inlineStr">
+        <is>
+          <t>Boykin, Jamee</t>
+        </is>
+      </c>
+      <c r="F93" s="87" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G93" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J93" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K93" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L93" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M93" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q93" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S93" s="87" t="inlineStr">
+        <is>
+          <t>02/13/26</t>
+        </is>
+      </c>
+      <c r="T93" s="90" t="n">
+        <v>46113</v>
+      </c>
+      <c r="V93" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" s="87" t="inlineStr">
+        <is>
+          <t>Nevler, Philip</t>
+        </is>
+      </c>
+      <c r="F94" s="87" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G94" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J94" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K94" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L94" s="89" t="n">
+        <v>995</v>
+      </c>
+      <c r="M94" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="89" t="n">
+        <v>995</v>
+      </c>
+      <c r="Q94" s="89" t="n">
+        <v>400</v>
+      </c>
+      <c r="R94" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="S94" s="87" t="inlineStr">
+        <is>
+          <t>12/01/25</t>
+        </is>
+      </c>
+      <c r="T94" s="90" t="n">
+        <v>39052</v>
+      </c>
+      <c r="V94" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" s="87" t="inlineStr">
+        <is>
+          <t>Martin, Bennie</t>
+        </is>
+      </c>
+      <c r="F95" s="87" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G95" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J95" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K95" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L95" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="M95" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Q95" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="S95" s="87" t="inlineStr">
+        <is>
+          <t>07/15/24</t>
+        </is>
+      </c>
+      <c r="T95" s="90" t="n">
+        <v>45122</v>
+      </c>
+      <c r="V95" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" s="87" t="inlineStr">
+        <is>
+          <t>Reinard (Bel), Amanda</t>
+        </is>
+      </c>
+      <c r="E96" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F96" s="87" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G96" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J96" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K96" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L96" s="89" t="n">
+        <v>1192</v>
+      </c>
+      <c r="M96" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="89" t="n">
+        <v>1192</v>
+      </c>
+      <c r="Q96" s="89" t="n">
+        <v>1192</v>
+      </c>
+      <c r="R96" s="89" t="n">
+        <v>1192</v>
+      </c>
+      <c r="S96" s="87" t="inlineStr">
+        <is>
+          <t>04/28/25</t>
+        </is>
+      </c>
+      <c r="T96" s="90" t="n">
+        <v>45775</v>
+      </c>
+      <c r="V96" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="C97" s="87" t="inlineStr">
+        <is>
+          <t>Jones (DePaul), Hope</t>
+        </is>
+      </c>
+      <c r="E97" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F97" s="87" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G97" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J97" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K97" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L97" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="M97" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="Q97" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="R97" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="S97" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="T97" s="90" t="n">
+        <v>45595</v>
+      </c>
+      <c r="V97" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" s="87" t="inlineStr">
+        <is>
+          <t>Williams-pearsall, Shavone</t>
+        </is>
+      </c>
+      <c r="F98" s="87" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G98" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="J98" s="88" t="n">
+        <v>1026</v>
+      </c>
+      <c r="K98" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L98" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="M98" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q98" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="S98" s="87" t="inlineStr">
+        <is>
+          <t>12/17/25</t>
+        </is>
+      </c>
+      <c r="T98" s="90" t="n">
+        <v>46023</v>
+      </c>
+      <c r="V98" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" s="87" t="inlineStr">
+        <is>
+          <t>Gelia (RACB), Gina</t>
+        </is>
+      </c>
+      <c r="E99" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F99" s="87" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G99" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J99" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K99" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L99" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="M99" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="P99" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q99" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="R99" s="89" t="n">
+        <v>76</v>
+      </c>
+      <c r="S99" s="87" t="inlineStr">
+        <is>
+          <t>11/01/24</t>
+        </is>
+      </c>
+      <c r="T99" s="90" t="n">
+        <v>45141</v>
+      </c>
+      <c r="V99" s="90" t="n">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="C100" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F100" s="87" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G100" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="J100" s="88" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K100" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L100" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M100" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N100" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="C101" s="87" t="inlineStr">
+        <is>
+          <t>Haslip, Brittany</t>
+        </is>
+      </c>
+      <c r="F101" s="87" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G101" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J101" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K101" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L101" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M101" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q101" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R101" s="89" t="n">
+        <v>55</v>
+      </c>
+      <c r="S101" s="87" t="inlineStr">
+        <is>
+          <t>07/01/25</t>
+        </is>
+      </c>
+      <c r="T101" s="90" t="n">
+        <v>45449</v>
+      </c>
+      <c r="V101" s="90" t="n">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" s="87" t="inlineStr">
+        <is>
+          <t>Madlock (BEL), Eaton</t>
+        </is>
+      </c>
+      <c r="E102" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F102" s="87" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G102" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="J102" s="88" t="n">
+        <v>1026</v>
+      </c>
+      <c r="K102" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L102" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="M102" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="Q102" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S102" s="87" t="inlineStr">
+        <is>
+          <t>02/01/25</t>
+        </is>
+      </c>
+      <c r="T102" s="90" t="n">
+        <v>45323</v>
+      </c>
+      <c r="V102" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="C103" s="87" t="inlineStr">
+        <is>
+          <t>Torres, Carmen (BMHA)</t>
+        </is>
+      </c>
+      <c r="E103" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F103" s="87" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G103" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J103" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K103" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L103" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M103" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q103" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="R103" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="S103" s="87" t="inlineStr">
+        <is>
+          <t>12/29/25</t>
+        </is>
+      </c>
+      <c r="T103" s="90" t="n">
+        <v>46023</v>
+      </c>
+      <c r="V103" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="C104" s="87" t="inlineStr">
+        <is>
+          <t>Patton (Evergreen), LaKaylea</t>
+        </is>
+      </c>
+      <c r="E104" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F104" s="87" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G104" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J104" s="88" t="n">
+        <v>1026</v>
+      </c>
+      <c r="K104" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L104" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="M104" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="Q104" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="R104" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="S104" s="87" t="inlineStr">
+        <is>
+          <t>10/29/24</t>
+        </is>
+      </c>
+      <c r="T104" s="90" t="n">
+        <v>45602</v>
+      </c>
+      <c r="V104" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="C105" s="87" t="inlineStr">
+        <is>
+          <t>Brown (BFNC), Chris</t>
+        </is>
+      </c>
+      <c r="E105" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F105" s="87" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G105" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J105" s="88" t="n">
+        <v>760</v>
+      </c>
+      <c r="K105" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L105" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="M105" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="Q105" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S105" s="87" t="inlineStr">
+        <is>
+          <t>10/06/25</t>
+        </is>
+      </c>
+      <c r="T105" s="90" t="n">
+        <v>45931</v>
+      </c>
+      <c r="V105" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="C106" s="87" t="inlineStr">
+        <is>
+          <t>McClerkin, Kierra</t>
+        </is>
+      </c>
+      <c r="F106" s="87" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G106" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="J106" s="88" t="n">
+        <v>1026</v>
+      </c>
+      <c r="K106" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L106" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M106" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q106" s="89" t="n">
+        <v>1360</v>
+      </c>
+      <c r="R106" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S106" s="87" t="inlineStr">
+        <is>
+          <t>08/01/25</t>
+        </is>
+      </c>
+      <c r="T106" s="90" t="n">
+        <v>42767</v>
+      </c>
+      <c r="V106" s="90" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="C107" s="87" t="inlineStr">
+        <is>
+          <t>Podgorny, Elizabeth</t>
+        </is>
+      </c>
+      <c r="F107" s="87" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G107" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J107" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K107" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L107" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="M107" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="Q107" s="89" t="n">
+        <v>585</v>
+      </c>
+      <c r="R107" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S107" s="87" t="inlineStr">
+        <is>
+          <t>12/01/25</t>
+        </is>
+      </c>
+      <c r="T107" s="90" t="n">
+        <v>42340</v>
+      </c>
+      <c r="V107" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="C108" s="87" t="inlineStr">
+        <is>
+          <t>Matthews, Yakeyda (RACB)</t>
+        </is>
+      </c>
+      <c r="E108" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F108" s="87" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G108" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J108" s="88" t="n">
+        <v>1076</v>
+      </c>
+      <c r="K108" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L108" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="M108" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q108" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R108" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="S108" s="87" t="inlineStr">
+        <is>
+          <t>09/29/25</t>
+        </is>
+      </c>
+      <c r="T108" s="90" t="n">
+        <v>45931</v>
+      </c>
+      <c r="V108" s="90" t="n">
+        <v>46660</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="C109" s="87" t="inlineStr">
+        <is>
+          <t>Funderburk, Khadia</t>
+        </is>
+      </c>
+      <c r="F109" s="87" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G109" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J109" s="88" t="n">
+        <v>1076</v>
+      </c>
+      <c r="K109" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L109" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M109" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q109" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="R109" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="S109" s="87" t="inlineStr">
+        <is>
+          <t>10/10/24</t>
+        </is>
+      </c>
+      <c r="T109" s="90" t="n">
+        <v>45580</v>
+      </c>
+      <c r="V109" s="90" t="n">
+        <v>46691</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="C110" s="87" t="inlineStr">
+        <is>
+          <t>Swann, Gina</t>
+        </is>
+      </c>
+      <c r="F110" s="87" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="G110" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J110" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K110" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L110" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M110" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q110" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R110" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S110" s="87" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+      <c r="T110" s="90" t="n">
+        <v>46143</v>
+      </c>
+      <c r="V110" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="C111" s="87" t="inlineStr">
+        <is>
+          <t>Moseley, Dara</t>
+        </is>
+      </c>
+      <c r="F111" s="87" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="G111" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J111" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K111" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L111" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="M111" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q111" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" s="89" t="n">
+        <v>55</v>
+      </c>
+      <c r="S111" s="87" t="inlineStr">
+        <is>
+          <t>07/01/25</t>
+        </is>
+      </c>
+      <c r="T111" s="90" t="n">
+        <v>45085</v>
+      </c>
+      <c r="V111" s="90" t="n">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="C112" s="87" t="inlineStr">
+        <is>
+          <t>Compton, Donald</t>
+        </is>
+      </c>
+      <c r="F112" s="87" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="G112" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J112" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K112" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L112" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="M112" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Q112" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="R112" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="S112" s="87" t="inlineStr">
+        <is>
+          <t>01/23/26</t>
+        </is>
+      </c>
+      <c r="T112" s="90" t="n">
+        <v>46053</v>
+      </c>
+      <c r="V112" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="C113" s="87" t="inlineStr">
+        <is>
+          <t>Reynolds (BEL), Warnette</t>
+        </is>
+      </c>
+      <c r="E113" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F113" s="87" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="G113" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J113" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K113" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L113" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="M113" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="Q113" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" s="89" t="n">
+        <v>150</v>
+      </c>
+      <c r="S113" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="T113" s="90" t="n">
+        <v>42552</v>
+      </c>
+      <c r="V113" s="90" t="n">
+        <v>46691</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="C114" s="87" t="inlineStr">
+        <is>
+          <t>Copeland (RACB), Takela</t>
+        </is>
+      </c>
+      <c r="E114" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F114" s="87" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G114" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J114" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K114" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L114" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M114" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q114" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S114" s="87" t="inlineStr">
+        <is>
+          <t>05/01/24</t>
+        </is>
+      </c>
+      <c r="T114" s="90" t="n">
+        <v>45413</v>
+      </c>
+      <c r="V114" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="C115" s="87" t="inlineStr">
+        <is>
+          <t>Holmes, Candice</t>
+        </is>
+      </c>
+      <c r="F115" s="87" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G115" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J115" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K115" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L115" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="M115" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="Q115" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R115" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="S115" s="87" t="inlineStr">
+        <is>
+          <t>05/01/24</t>
+        </is>
+      </c>
+      <c r="T115" s="90" t="n">
+        <v>44438</v>
+      </c>
+      <c r="V115" s="90" t="n">
+        <v>45777</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="C116" s="87" t="inlineStr">
+        <is>
+          <t>McCarter, Lynea</t>
+        </is>
+      </c>
+      <c r="F116" s="87" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G116" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J116" s="88" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K116" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L116" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="M116" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q116" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R116" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S116" s="87" t="inlineStr">
+        <is>
+          <t>06/09/25</t>
+        </is>
+      </c>
+      <c r="T116" s="90" t="n">
+        <v>45818</v>
+      </c>
+      <c r="V116" s="90" t="n">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="C117" s="87" t="inlineStr">
+        <is>
+          <t>Garner, Antwan</t>
+        </is>
+      </c>
+      <c r="F117" s="87" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G117" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J117" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K117" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L117" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="M117" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Q117" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="R117" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="S117" s="87" t="inlineStr">
+        <is>
+          <t>02/17/26</t>
+        </is>
+      </c>
+      <c r="T117" s="90" t="n">
+        <v>46082</v>
+      </c>
+      <c r="V117" s="90" t="n">
+        <v>46478</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="C118" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F118" s="87" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G118" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J118" s="88" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K118" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L118" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M118" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N118" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="C119" s="87" t="inlineStr">
+        <is>
+          <t>Conway, Christian</t>
+        </is>
+      </c>
+      <c r="F119" s="87" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G119" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J119" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K119" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L119" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M119" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q119" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="S119" s="87" t="inlineStr">
+        <is>
+          <t>05/01/24</t>
+        </is>
+      </c>
+      <c r="T119" s="90" t="n">
+        <v>45047</v>
+      </c>
+      <c r="V119" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="C120" s="87" t="inlineStr">
+        <is>
+          <t>Battaglia (TSI), Anthony</t>
+        </is>
+      </c>
+      <c r="E120" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F120" s="87" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G120" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J120" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K120" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L120" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="M120" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q120" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R120" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S120" s="87" t="inlineStr">
+        <is>
+          <t>12/01/24</t>
+        </is>
+      </c>
+      <c r="T120" s="90" t="n">
+        <v>44516</v>
+      </c>
+      <c r="V120" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="C121" s="87" t="inlineStr">
+        <is>
+          <t>Flores Rosario, Gysellys</t>
+        </is>
+      </c>
+      <c r="F121" s="87" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G121" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J121" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K121" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L121" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="M121" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q121" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="R121" s="89" t="n">
+        <v>80</v>
+      </c>
+      <c r="S121" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="T121" s="90" t="n">
+        <v>45370</v>
+      </c>
+      <c r="V121" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="C122" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="F122" s="87" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="G122" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J122" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K122" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L122" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M122" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="N122" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="C123" s="87" t="inlineStr">
+        <is>
+          <t>Daniels, Samantha</t>
+        </is>
+      </c>
+      <c r="F123" s="87" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G123" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J123" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K123" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L123" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M123" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q123" s="89" t="n">
+        <v>850</v>
+      </c>
+      <c r="R123" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="S123" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="T123" s="90" t="n">
+        <v>43647</v>
+      </c>
+      <c r="V123" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="C124" s="87" t="inlineStr">
+        <is>
+          <t>Pimental (RACB), Janet</t>
+        </is>
+      </c>
+      <c r="E124" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F124" s="87" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="G124" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J124" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K124" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L124" s="89" t="n">
+        <v>1395</v>
+      </c>
+      <c r="M124" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="89" t="n">
+        <v>1395</v>
+      </c>
+      <c r="Q124" s="89" t="n">
+        <v>467</v>
+      </c>
+      <c r="R124" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="S124" s="87" t="inlineStr">
+        <is>
+          <t>03/01/25</t>
+        </is>
+      </c>
+      <c r="T124" s="90" t="n">
+        <v>38763</v>
+      </c>
+      <c r="V124" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="C125" s="87" t="inlineStr">
+        <is>
+          <t>Allen, Joseph</t>
+        </is>
+      </c>
+      <c r="F125" s="87" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="G125" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J125" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K125" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L125" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M125" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q125" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R125" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="S125" s="87" t="inlineStr">
+        <is>
+          <t>12/08/25</t>
+        </is>
+      </c>
+      <c r="T125" s="90" t="n">
+        <v>46023</v>
+      </c>
+      <c r="V125" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="C126" s="87" t="inlineStr">
+        <is>
+          <t>Johnson, Theressa</t>
+        </is>
+      </c>
+      <c r="F126" s="87" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G126" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J126" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K126" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L126" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="M126" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="Q126" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="R126" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="S126" s="87" t="inlineStr">
+        <is>
+          <t>02/01/26</t>
+        </is>
+      </c>
+      <c r="T126" s="90" t="n">
+        <v>44927</v>
+      </c>
+      <c r="V126" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="C127" s="87" t="inlineStr">
+        <is>
+          <t>Ross, Courtney</t>
+        </is>
+      </c>
+      <c r="F127" s="87" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G127" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J127" s="88" t="n">
+        <v>1550</v>
+      </c>
+      <c r="K127" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L127" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M127" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q127" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="R127" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="S127" s="87" t="inlineStr">
+        <is>
+          <t>08/01/25</t>
+        </is>
+      </c>
+      <c r="T127" s="90" t="n">
+        <v>45519</v>
+      </c>
+      <c r="V127" s="90" t="n">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="C128" s="87" t="inlineStr">
+        <is>
+          <t>Smith, Paige</t>
+        </is>
+      </c>
+      <c r="F128" s="87" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="G128" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="J128" s="88" t="n">
+        <v>1076</v>
+      </c>
+      <c r="K128" s="89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="L128" s="89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="M128" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q128" s="89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="R128" s="89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="S128" s="87" t="inlineStr">
+        <is>
+          <t>05/29/25</t>
+        </is>
+      </c>
+      <c r="T128" s="90" t="n">
+        <v>45806</v>
+      </c>
+      <c r="V128" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" s="87" t="inlineStr">
+        <is>
+          <t>Massey (RACB), John</t>
+        </is>
+      </c>
+      <c r="E129" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F129" s="87" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="G129" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J129" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K129" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L129" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M129" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q129" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="S129" s="87" t="inlineStr">
+        <is>
+          <t>08/01/25</t>
+        </is>
+      </c>
+      <c r="T129" s="90" t="n">
+        <v>41944</v>
+      </c>
+      <c r="V129" s="90" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="C130" s="87" t="inlineStr">
+        <is>
+          <t>Herby (RACB), Mary</t>
+        </is>
+      </c>
+      <c r="E130" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F130" s="87" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="G130" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="J130" s="88" t="n">
+        <v>904</v>
+      </c>
+      <c r="K130" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L130" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="M130" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="Q130" s="89" t="n">
+        <v>148</v>
+      </c>
+      <c r="R130" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="S130" s="87" t="inlineStr">
+        <is>
+          <t>02/01/25</t>
+        </is>
+      </c>
+      <c r="T130" s="90" t="n">
+        <v>36830</v>
+      </c>
+      <c r="V130" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="J131" s="88" t="n">
+        <v>117872</v>
+      </c>
+      <c r="K131" s="89" t="n">
+        <v>163520</v>
+      </c>
+      <c r="L131" s="89" t="n">
+        <v>156848</v>
+      </c>
+      <c r="M131" s="89" t="n">
+        <v>17225</v>
+      </c>
+      <c r="N131" s="89" t="n">
+        <v>825</v>
+      </c>
+      <c r="P131" s="89" t="n">
+        <v>140448</v>
+      </c>
+      <c r="Q131" s="89" t="n">
+        <v>93950</v>
+      </c>
+      <c r="R131" s="89" t="n">
+        <v>66084</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Totals for </t>
+        </is>
+      </c>
+      <c r="D132" s="87" t="inlineStr">
+        <is>
+          <t>Delsan Court</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="E133" s="87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="J135" s="87" t="inlineStr">
+        <is>
+          <t>Sq Ft</t>
+        </is>
+      </c>
+      <c r="K135" s="87" t="inlineStr">
+        <is>
+          <t>Market 
+Rent</t>
+        </is>
+      </c>
+      <c r="L135" s="87" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="M135" s="87" t="inlineStr">
+        <is>
+          <t>Vacancy 
+Loss</t>
+        </is>
+      </c>
+      <c r="N135" s="87" t="inlineStr">
+        <is>
+          <t>Misc 
+Charges</t>
+        </is>
+      </c>
+      <c r="P135" s="87" t="inlineStr">
+        <is>
+          <t>Total 
+Charges</t>
+        </is>
+      </c>
+      <c r="Q135" s="87" t="inlineStr">
+        <is>
+          <t>Security 
+Deposit</t>
+        </is>
+      </c>
+      <c r="R135" s="87" t="inlineStr">
+        <is>
+          <t>Increase 
+Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="J136" s="88" t="n">
+        <v>117872</v>
+      </c>
+      <c r="K136" s="89" t="n">
+        <v>163520</v>
+      </c>
+      <c r="L136" s="89" t="n">
+        <v>156848</v>
+      </c>
+      <c r="M136" s="89" t="n">
+        <v>17225</v>
+      </c>
+      <c r="N136" s="89" t="n">
+        <v>825</v>
+      </c>
+      <c r="P136" s="89" t="n">
+        <v>140448</v>
+      </c>
+      <c r="Q136" s="89" t="n">
+        <v>93950</v>
+      </c>
+      <c r="R136" s="89" t="n">
+        <v>66084</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="87" t="inlineStr">
+        <is>
+          <t>Report Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="87" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="O140" s="87" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="87" t="inlineStr">
+        <is>
+          <t>Total Possible Rent</t>
+        </is>
+      </c>
+      <c r="O141" s="87" t="inlineStr">
+        <is>
+          <t>156,848.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="87" t="inlineStr">
+        <is>
+          <t>Vacancy Rent</t>
+        </is>
+      </c>
+      <c r="O142" s="87" t="inlineStr">
+        <is>
+          <t>17,225.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="87" t="inlineStr">
+        <is>
+          <t>Occupied Unit Rent</t>
+        </is>
+      </c>
+      <c r="O143" s="87" t="inlineStr">
+        <is>
+          <t>139,623.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="87" t="inlineStr">
+        <is>
+          <t># of Units</t>
+        </is>
+      </c>
+      <c r="O144" s="87" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="87" t="inlineStr">
+        <is>
+          <t>Vacant Units</t>
+        </is>
+      </c>
+      <c r="O145" s="87" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="87" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="O146" s="87" t="inlineStr">
+        <is>
+          <t>89.52%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="524">
+    <mergeCell ref="N101:O101"/>
+    <mergeCell ref="N113:O113"/>
+    <mergeCell ref="V73:W73"/>
+    <mergeCell ref="N76:O76"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="V100:W100"/>
+    <mergeCell ref="N100:O100"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="N94:O94"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="A142:N142"/>
+    <mergeCell ref="O146:W146"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="V102:W102"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="N77:O77"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="V84:W84"/>
+    <mergeCell ref="V127:W127"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="A145:N145"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="V128:W128"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="N87:O87"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="N89:O89"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="N121:O121"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="N115:O115"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="V99:W99"/>
+    <mergeCell ref="N102:O102"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="V74:W74"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="V39:W39"/>
+    <mergeCell ref="V110:W110"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="N116:O116"/>
+    <mergeCell ref="V103:W103"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="V118:W118"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="V65:W65"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="V129:W129"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="V94:W94"/>
+    <mergeCell ref="V121:W121"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="N96:O96"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="A146:N146"/>
+    <mergeCell ref="V87:W87"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="V89:W89"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="V49:W49"/>
+    <mergeCell ref="A3:W3"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="V120:W120"/>
+    <mergeCell ref="N123:O123"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="A141:N141"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="V113:W113"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="V124:W124"/>
+    <mergeCell ref="N124:O124"/>
+    <mergeCell ref="N118:O118"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="V55:W55"/>
+    <mergeCell ref="V126:W126"/>
+    <mergeCell ref="N126:O126"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="N109:O109"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="N71:O71"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="V60:W60"/>
+    <mergeCell ref="V45:W45"/>
+    <mergeCell ref="N119:O119"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="V57:W57"/>
+    <mergeCell ref="N114:O114"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="V86:W86"/>
+    <mergeCell ref="V42:W42"/>
+    <mergeCell ref="V58:W58"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="N130:O130"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="N117:O117"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="V70:W70"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G91:H91"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="V109:W109"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="V47:W47"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="V101:W101"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="V76:W76"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="V48:W48"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="N122:O122"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="V77:W77"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="N92:O92"/>
+    <mergeCell ref="N67:O67"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="V66:W66"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="V53:W53"/>
+    <mergeCell ref="V46:W46"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="V95:W95"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="V61:W61"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="N135:O135"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="G130:H130"/>
+    <mergeCell ref="V79:W79"/>
+    <mergeCell ref="G122:H122"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="V115:W115"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="V123:W123"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="N82:O82"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="V130:W130"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="N108:O108"/>
+    <mergeCell ref="V92:W92"/>
+    <mergeCell ref="N95:O95"/>
+    <mergeCell ref="V67:W67"/>
+    <mergeCell ref="G120:H120"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="V97:W97"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="N97:O97"/>
+    <mergeCell ref="V69:W69"/>
+    <mergeCell ref="N72:O72"/>
+    <mergeCell ref="V96:W96"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="O142:W142"/>
+    <mergeCell ref="N136:O136"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="V98:W98"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="O144:W144"/>
+    <mergeCell ref="A138:V138"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="N88:O88"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="N90:O90"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="N83:O83"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="V116:W116"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N91:O91"/>
+    <mergeCell ref="V82:W82"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="N85:O85"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="V111:W111"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="V44:W44"/>
+    <mergeCell ref="G121:H121"/>
+    <mergeCell ref="V108:W108"/>
+    <mergeCell ref="N111:O111"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="D132:I132"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="G123:H123"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="O145:W145"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="N79:O79"/>
+    <mergeCell ref="V114:W114"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="A143:N143"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="V88:W88"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="N93:O93"/>
+    <mergeCell ref="V117:W117"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="V83:W83"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="V119:W119"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="O140:W140"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="N104:O104"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="V38:W38"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="N112:O112"/>
+    <mergeCell ref="N106:O106"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="V105:W105"/>
+    <mergeCell ref="N105:O105"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="V63:W63"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="V107:W107"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="N107:O107"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="V104:W104"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="A144:N144"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="O141:W141"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="V122:W122"/>
+    <mergeCell ref="N110:O110"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="O143:W143"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="N125:O125"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="V59:W59"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="N127:O127"/>
+    <mergeCell ref="V40:W40"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="N64:O64"/>
+    <mergeCell ref="N120:O120"/>
+    <mergeCell ref="G92:H92"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="V54:W54"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="N128:O128"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="V41:W41"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="A140:N140"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="V72:W72"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="N103:O103"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="V125:W125"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="V90:W90"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="V62:W62"/>
+    <mergeCell ref="N65:O65"/>
+    <mergeCell ref="V56:W56"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="V43:W43"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N63:O63"/>
+    <mergeCell ref="N129:O129"/>
+    <mergeCell ref="V91:W91"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="V85:W85"/>
+    <mergeCell ref="N131:O131"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="N84:O84"/>
+    <mergeCell ref="V75:W75"/>
+    <mergeCell ref="N78:O78"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="V50:W50"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="V64:W64"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="V93:W93"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="G118:H118"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V112:W112"/>
+    <mergeCell ref="V106:W106"/>
+    <mergeCell ref="V81:W81"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="V78:W78"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="G124:H124"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="N99:O99"/>
+    <mergeCell ref="G119:H119"/>
+    <mergeCell ref="V71:W71"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="N36:O36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>